--- a/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9422_escuela-centro-educ-rep-mexicana_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{765ABC87-E6AA-4DB0-A4E8-6F0A14E7E505}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF3CD6C8-7FBA-4C79-B5A7-37BC05CB6795}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C91D4101-6F40-4C30-A060-235430182E34}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE31609D-9E37-4139-89F7-F2B2F04FB707}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7B7C316-CFC7-4817-8035-E9E63BC7A602}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B89C614-C9D5-4044-8949-621599894E44}"/>
 </file>